--- a/inst/examples/onco/spec/tables.xlsx
+++ b/inst/examples/onco/spec/tables.xlsx
@@ -1940,7 +1940,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -2056,6 +2056,12 @@
     <t xml:space="preserve">Subjects with at least one TEAE</t>
   </si>
   <si>
+    <t xml:space="preserve">T-14-3-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
     <t xml:space="preserve">variable</t>
   </si>
   <si>
@@ -2131,6 +2137,42 @@
     <t xml:space="preserve">Disease control rate (CR + PR + SD)</t>
   </si>
   <si>
+    <t xml:space="preserve">ANY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any TEAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any treatment-related TEAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any TEAE of CTCAE grade 3 or higher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any serious TEAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any TEAE leading to discontinuation of study drug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any TEAE leading to death</t>
+  </si>
+  <si>
     <t xml:space="preserve">M</t>
   </si>
   <si>
@@ -2383,6 +2425,9 @@
     <t xml:space="preserve">4</t>
   </si>
   <si>
+    <t xml:space="preserve">group</t>
+  </si>
+  <si>
     <t xml:space="preserve">border</t>
   </si>
   <si>
@@ -2528,6 +2573,9 @@
   </si>
   <si>
     <t xml:space="preserve">Preferred term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subjects with</t>
   </si>
   <si>
     <t xml:space="preserve">spec_version</t>
@@ -2895,31 +2943,31 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="E1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="H1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="I1" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="J1" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="K1" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2939,28 +2987,28 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="E1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1" t="s">
         <v>185</v>
       </c>
-      <c r="F1" t="s">
-        <v>170</v>
-      </c>
       <c r="G1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="H1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="I1" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2">
@@ -2968,10 +3016,10 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -2985,16 +3033,16 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
@@ -3006,14 +3054,14 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
@@ -3025,16 +3073,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E5" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="F5"/>
       <c r="G5"/>
@@ -3046,10 +3094,10 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -3063,16 +3111,16 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F7"/>
       <c r="G7"/>
@@ -3084,14 +3132,14 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F8"/>
       <c r="G8"/>
@@ -3103,16 +3151,16 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
@@ -3124,14 +3172,14 @@
         <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
@@ -3143,16 +3191,16 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E11" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>
@@ -3164,14 +3212,14 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F12"/>
       <c r="G12"/>
@@ -3183,21 +3231,99 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E13" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="F13"/>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" t="s">
+        <v>204</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E17" t="s">
+        <v>207</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3221,10 +3347,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3420,6 +3546,41 @@
       <c r="X4"/>
       <c r="Y4"/>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3437,22 +3598,22 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -3460,10 +3621,10 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -3477,10 +3638,10 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -3494,16 +3655,16 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
@@ -3513,10 +3674,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -3530,10 +3691,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -3547,16 +3708,16 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F7"/>
       <c r="G7"/>
@@ -3566,10 +3727,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -3583,10 +3744,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -3600,10 +3761,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -3611,6 +3772,108 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3629,7 +3892,7 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3638,7 +3901,7 @@
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
@@ -3646,13 +3909,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3663,13 +3926,13 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -3680,13 +3943,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3697,13 +3960,13 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -3714,13 +3977,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -3731,13 +3994,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -3748,13 +4011,13 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -3777,25 +4040,25 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -3803,18 +4066,18 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H2"/>
     </row>
@@ -3823,18 +4086,18 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H3"/>
     </row>
@@ -3843,18 +4106,18 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H4"/>
     </row>
@@ -3863,31 +4126,31 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H5"/>
     </row>
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
@@ -3897,15 +4160,15 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -3915,15 +4178,15 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -3945,13 +4208,13 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3971,91 +4234,91 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="I1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="L1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="O1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="P1" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="Q1" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="R1" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="S1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="T1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="U1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="V1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="W1" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="X1" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="Y1" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="Z1" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="AA1" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="AB1" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="AC1" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="AD1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
@@ -4063,10 +4326,10 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -4080,19 +4343,19 @@
       <c r="M2"/>
       <c r="N2"/>
       <c r="O2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="P2"/>
       <c r="Q2"/>
       <c r="R2"/>
       <c r="S2"/>
       <c r="T2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="U2"/>
       <c r="V2"/>
       <c r="W2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="X2"/>
       <c r="Y2"/>
@@ -4107,10 +4370,10 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -4124,19 +4387,19 @@
       <c r="M3"/>
       <c r="N3"/>
       <c r="O3" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3"/>
       <c r="S3"/>
       <c r="T3" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="U3"/>
       <c r="V3"/>
       <c r="W3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="X3"/>
       <c r="Y3"/>
@@ -4151,10 +4414,10 @@
         <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -4168,19 +4431,19 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4"/>
       <c r="S4"/>
       <c r="T4" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="U4"/>
       <c r="V4"/>
       <c r="W4" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="X4"/>
       <c r="Y4"/>
@@ -4189,6 +4452,44 @@
       <c r="AB4"/>
       <c r="AC4"/>
       <c r="AD4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4207,19 +4508,19 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C1" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="D1" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E1" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="F1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
@@ -4227,10 +4528,10 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -4241,10 +4542,10 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -4255,10 +4556,10 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -4269,10 +4570,10 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -4283,10 +4584,10 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -4297,14 +4598,42 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4323,97 +4652,97 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C1" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D1" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F1" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="H1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="I1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="J1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K1" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="L1" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="M1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="N1" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="O1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="P1" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="Q1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="R1" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="S1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="T1" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="U1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="V1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="W1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="X1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="Y1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="Z1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="AA1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="AB1" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="AC1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="AD1" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="AE1" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="AF1" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
